--- a/Funding_impactAnalysis/data/HIV_Syphilsdualkit_Subcounty.xlsx
+++ b/Funding_impactAnalysis/data/HIV_Syphilsdualkit_Subcounty.xlsx
@@ -17,7 +17,7 @@
     <t xml:space="preserve">county</t>
   </si>
   <si>
-    <t xml:space="preserve">sub_county</t>
+    <t xml:space="preserve">Sub county</t>
   </si>
   <si>
     <t xml:space="preserve">pre_funding_cut_count_median_IQR</t>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">Baringo County</t>
   </si>
   <si>
-    <t xml:space="preserve">Baringo Central</t>
+    <t xml:space="preserve">baringo central</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-1]</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">5.26 [0-8]</t>
   </si>
   <si>
-    <t xml:space="preserve">Baringo North</t>
+    <t xml:space="preserve">baringo north</t>
   </si>
   <si>
     <t xml:space="preserve">2 [1-3]</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">7.69 [4.55-12]</t>
   </si>
   <si>
-    <t xml:space="preserve">Marigat</t>
+    <t xml:space="preserve">marigat</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-1.25]</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Bomet County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bomet Central</t>
+    <t xml:space="preserve">bomet central</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-3.25]</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">11.11 [8-14.81]</t>
   </si>
   <si>
-    <t xml:space="preserve">Bomet East</t>
+    <t xml:space="preserve">bomet east</t>
   </si>
   <si>
     <t xml:space="preserve">4.77 [0-10.44]</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">5.56 [0-10.53]</t>
   </si>
   <si>
-    <t xml:space="preserve">Chepalungu</t>
+    <t xml:space="preserve">chepalungu</t>
   </si>
   <si>
     <t xml:space="preserve">2 [1-4]</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">11.11 [9.09-16]</t>
   </si>
   <si>
-    <t xml:space="preserve">Konoin</t>
+    <t xml:space="preserve">konoin</t>
   </si>
   <si>
     <t xml:space="preserve">1 [1-2]</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">4.55 [3.12-11.76]</t>
   </si>
   <si>
-    <t xml:space="preserve">Sotik</t>
+    <t xml:space="preserve">sotik</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [0-2]</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Bungoma County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bumula</t>
+    <t xml:space="preserve">bumula</t>
   </si>
   <si>
     <t xml:space="preserve">3 [1-4]</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">16.67 [6.25-31.25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Cheptais</t>
+    <t xml:space="preserve">cheptais</t>
   </si>
   <si>
     <t xml:space="preserve">3.85 [0-26.67]</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">36.67 [17.27-51.79]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kabuchai</t>
+    <t xml:space="preserve">kabuchai</t>
   </si>
   <si>
     <t xml:space="preserve">24.75 [6.25-42.86]</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">5.56 [0-16.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kanduyi</t>
+    <t xml:space="preserve">kanduyi</t>
   </si>
   <si>
     <t xml:space="preserve">3 [1-5.25]</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">9.09 [5.41-19.44]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kimilili</t>
+    <t xml:space="preserve">kimilili</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-1]</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">6.67 [0-7.14]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mt Elgon</t>
+    <t xml:space="preserve">mt. elgon</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 [0-2]</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">5.41 [0-6.68]</t>
   </si>
   <si>
-    <t xml:space="preserve">Sirisia</t>
+    <t xml:space="preserve">sirisia</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-14.29]</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">14.29 [6.25-23.08]</t>
   </si>
   <si>
-    <t xml:space="preserve">Webuye East</t>
+    <t xml:space="preserve">webuye east</t>
   </si>
   <si>
     <t xml:space="preserve">2 [1-2]</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">Busia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bunyala</t>
+    <t xml:space="preserve">bunyala</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-12.95]</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">11.11 [0-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Butula</t>
+    <t xml:space="preserve">butula</t>
   </si>
   <si>
     <t xml:space="preserve">7.42 [0-17.19]</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">22.22 [16.67-45.45]</t>
   </si>
   <si>
-    <t xml:space="preserve">Matayos</t>
+    <t xml:space="preserve">matayos</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-0.25]</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">21.43 [15.38-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nambale</t>
+    <t xml:space="preserve">nambale</t>
   </si>
   <si>
     <t xml:space="preserve">9.09 [0-14.88]</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">15.38 [11.11-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Teso Central</t>
+    <t xml:space="preserve">teso central</t>
   </si>
   <si>
     <t xml:space="preserve">9.55 [0-18.64]</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0 [0-12.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Teso South</t>
+    <t xml:space="preserve">teso south</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-16.67]</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">Elgeyo Marakwet County</t>
   </si>
   <si>
-    <t xml:space="preserve">Keiyo North</t>
+    <t xml:space="preserve">keiyo north</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 [0-1]</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">25 [16.67-33.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Marakwet East</t>
+    <t xml:space="preserve">marakwet east</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-2.25]</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">9.09 [0-16.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Marakwet West</t>
+    <t xml:space="preserve">marakwet west</t>
   </si>
   <si>
     <t xml:space="preserve">7.69 [0-14.58]</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">Embu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Embu North</t>
+    <t xml:space="preserve">embu north</t>
   </si>
   <si>
     <t xml:space="preserve">8.71 [0-20]</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">9.17 [0-17.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Embu west</t>
+    <t xml:space="preserve">embu west</t>
   </si>
   <si>
     <t xml:space="preserve">2 [1-3.25]</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">18.75 [15.38-23.53]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mbeere North</t>
+    <t xml:space="preserve">mbeere north</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-14.88]</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">11.11 [6.67-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mbeere South</t>
+    <t xml:space="preserve">mbeere south</t>
   </si>
   <si>
     <t xml:space="preserve">7.42 [0-18.64]</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">Homa Bay County</t>
   </si>
   <si>
-    <t xml:space="preserve">Rachuonyo East</t>
+    <t xml:space="preserve">rachuonyo east</t>
   </si>
   <si>
     <t xml:space="preserve">2.94 [0-18.27]</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">21.05 [6.67-33.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Rachuonyo North </t>
+    <t xml:space="preserve">rachuonyo north</t>
   </si>
   <si>
     <t xml:space="preserve">2 [2-6]</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">9.09 [5.41-19.35]</t>
   </si>
   <si>
-    <t xml:space="preserve">Suba North</t>
+    <t xml:space="preserve">suba north</t>
   </si>
   <si>
     <t xml:space="preserve">11.81 [0-27.68]</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">12.5 [0-23.08]</t>
   </si>
   <si>
-    <t xml:space="preserve">Suba South</t>
+    <t xml:space="preserve">suba south</t>
   </si>
   <si>
     <t xml:space="preserve">4.55 [0-7.77]</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">Kajiado County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kajiado Central</t>
+    <t xml:space="preserve">kajiado central</t>
   </si>
   <si>
     <t xml:space="preserve">5.72 [0-11.11]</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">18.75 [16.67-22.73]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kajiado East</t>
+    <t xml:space="preserve">kajiado east</t>
   </si>
   <si>
     <t xml:space="preserve">7.5 [0-20]</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">20 [10.53-29.41]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kajiado North</t>
+    <t xml:space="preserve">kajiado north</t>
   </si>
   <si>
     <t xml:space="preserve">8.33 [0-21.59]</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">8.33 [7.69-14.29]</t>
   </si>
   <si>
-    <t xml:space="preserve">Loitokitok</t>
+    <t xml:space="preserve">loitokitok</t>
   </si>
   <si>
     <t xml:space="preserve">14.58 [4.09-25]</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">Kakamega County</t>
   </si>
   <si>
-    <t xml:space="preserve">Butere</t>
+    <t xml:space="preserve">butere</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-7.5]</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">20 [17.65-30]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ikolomani</t>
+    <t xml:space="preserve">ikolomani</t>
   </si>
   <si>
     <t xml:space="preserve">5.72 [0-10.53]</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">21.43 [18.75-30]</t>
   </si>
   <si>
-    <t xml:space="preserve">Khwisero</t>
+    <t xml:space="preserve">khwisero</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 [0-2.25]</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">8.7 [0-13.64]</t>
   </si>
   <si>
-    <t xml:space="preserve">Likuyani</t>
+    <t xml:space="preserve">likuyani</t>
   </si>
   <si>
     <t xml:space="preserve">13.81 [7.02-23.56]</t>
   </si>
   <si>
-    <t xml:space="preserve">Lurambi</t>
+    <t xml:space="preserve">lurambi</t>
   </si>
   <si>
     <t xml:space="preserve">1 [1-3]</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">18.75 [16.67-28.57]</t>
   </si>
   <si>
-    <t xml:space="preserve">Malava</t>
+    <t xml:space="preserve">malava</t>
   </si>
   <si>
     <t xml:space="preserve">4 [1-5.25]</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">42.81 [24.31-50]</t>
   </si>
   <si>
-    <t xml:space="preserve">Matungu</t>
+    <t xml:space="preserve">matungu</t>
   </si>
   <si>
     <t xml:space="preserve">10.1 [0-22.92]</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">22.22 [12.5-37.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mumias West</t>
+    <t xml:space="preserve">mumias west</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-8.33]</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">7.69 [0-11.11]</t>
   </si>
   <si>
-    <t xml:space="preserve">Navakholo</t>
+    <t xml:space="preserve">navakholo</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [1-2]</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">33.33 [7.69-37.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Shinyalu</t>
+    <t xml:space="preserve">shinyalu</t>
   </si>
   <si>
     <t xml:space="preserve">5 [4-6]</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">Kericho County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ainamoi</t>
+    <t xml:space="preserve">ainamoi</t>
   </si>
   <si>
     <t xml:space="preserve">4.55 [0-10.62]</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">14.81 [13.04-16]</t>
   </si>
   <si>
-    <t xml:space="preserve">Bureti</t>
+    <t xml:space="preserve">buret</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [1-3]</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">17.65 [11.76-22.58]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kipkelion West</t>
+    <t xml:space="preserve">kipkelion west</t>
   </si>
   <si>
     <t xml:space="preserve">10 [7.14-25]</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">Kiambu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Githunguri</t>
+    <t xml:space="preserve">githunguri</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-3]</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">8.33 [0-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kikuyu</t>
+    <t xml:space="preserve">kikuyu</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-0]</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">5 [0-14.88]</t>
   </si>
   <si>
-    <t xml:space="preserve">Lari</t>
+    <t xml:space="preserve">lari</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-13.39]</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">Kilifi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ganze</t>
+    <t xml:space="preserve">ganze</t>
   </si>
   <si>
     <t xml:space="preserve">7.11 [0-15.71]</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">11.11 [5-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaloleni</t>
+    <t xml:space="preserve">kaloleni</t>
   </si>
   <si>
     <t xml:space="preserve">5.88 [0-9.32]</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">7.14 [0-12.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilifi North</t>
+    <t xml:space="preserve">kilifi north</t>
   </si>
   <si>
     <t xml:space="preserve">5.56 [0-11.9]</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">14.29 [10.34-18.75]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilifi South</t>
+    <t xml:space="preserve">kilifi south</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-1.5]</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">20 [9.09-26.32]</t>
   </si>
   <si>
-    <t xml:space="preserve">Magarini</t>
+    <t xml:space="preserve">magarini</t>
   </si>
   <si>
     <t xml:space="preserve">6 [4-6]</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">16.67 [12.5-18.75]</t>
   </si>
   <si>
-    <t xml:space="preserve">Malindi</t>
+    <t xml:space="preserve">malindi</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0.75-2]</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">15 [8.33-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Rabai</t>
+    <t xml:space="preserve">rabai</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-7.44]</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">Kirinyaga County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirinyaga Central</t>
+    <t xml:space="preserve">kirinyaga central</t>
   </si>
   <si>
     <t xml:space="preserve">6.67 [0-12.5]</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">18.18 [7.69-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirinyaga East</t>
+    <t xml:space="preserve">kirinyaga east</t>
   </si>
   <si>
     <t xml:space="preserve">7.18 [0-12.95]</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">16.67 [10-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirinyaga North/Mwea West</t>
+    <t xml:space="preserve">kirinyaga north/mwea west</t>
   </si>
   <si>
     <t xml:space="preserve">8.01 [0-17.5]</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">12.5 [8.33-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirinyaga West</t>
+    <t xml:space="preserve">kirinyaga west</t>
   </si>
   <si>
     <t xml:space="preserve">6.25 [0-16.67]</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">Kisii County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bomachoge Chache</t>
+    <t xml:space="preserve">bomachoge chache</t>
   </si>
   <si>
     <t xml:space="preserve">10 [0-15.38]</t>
   </si>
   <si>
-    <t xml:space="preserve">Bonchari</t>
+    <t xml:space="preserve">bonchari</t>
   </si>
   <si>
     <t xml:space="preserve">10 [0-21.83]</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">11.76 [6.67-18.75]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitutu Chache North</t>
+    <t xml:space="preserve">kitutu chache north</t>
   </si>
   <si>
     <t xml:space="preserve">11.11 [0-26.14]</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">14.58 [0-30.83]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitutu Chache South</t>
+    <t xml:space="preserve">kitutu chache south</t>
   </si>
   <si>
     <t xml:space="preserve">8.71 [5.56-16.91]</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">17.69 [10.54-22.8]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyaribari Chache</t>
+    <t xml:space="preserve">nyaribari chache</t>
   </si>
   <si>
     <t xml:space="preserve">5.72 [0-16.67]</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">11.76 [5.88-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyaribari Masaba</t>
+    <t xml:space="preserve">nyaribari masaba</t>
   </si>
   <si>
     <t xml:space="preserve">8.33 [0-16.67]</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">11.11 [4-18.18]</t>
   </si>
   <si>
-    <t xml:space="preserve">South Mugirango</t>
+    <t xml:space="preserve">south mugirango</t>
   </si>
   <si>
     <t xml:space="preserve">7.42 [0-14.29]</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">Kisumu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kadibo</t>
+    <t xml:space="preserve">kadibo</t>
   </si>
   <si>
     <t xml:space="preserve">16.67 [11.11-50]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kisumu Central</t>
+    <t xml:space="preserve">kisumu central</t>
   </si>
   <si>
     <t xml:space="preserve">3 [2-3]</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">11.54 [10-17.86]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kisumu East</t>
+    <t xml:space="preserve">kisumu east</t>
   </si>
   <si>
     <t xml:space="preserve">14.84 [6.67-21.84]</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">17.65 [6.25-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kisumu West</t>
+    <t xml:space="preserve">kisumu west</t>
   </si>
   <si>
     <t xml:space="preserve">8.2 [0-15.1]</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">23.08 [5.88-29.41]</t>
   </si>
   <si>
-    <t xml:space="preserve">Muhoroni</t>
+    <t xml:space="preserve">muhoroni</t>
   </si>
   <si>
     <t xml:space="preserve">2 [0-4]</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">14.81 [11.54-26.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyando</t>
+    <t xml:space="preserve">nyando</t>
   </si>
   <si>
     <t xml:space="preserve">3.57 [0-17.5]</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">14.29 [6.67-16.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Seme</t>
+    <t xml:space="preserve">seme</t>
   </si>
   <si>
     <t xml:space="preserve">5 [2-6]</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">Kitui County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui Central</t>
+    <t xml:space="preserve">kitui central</t>
   </si>
   <si>
     <t xml:space="preserve">13.04 [7.69-16.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui East</t>
+    <t xml:space="preserve">kitui east</t>
   </si>
   <si>
     <t xml:space="preserve">17.91 [0-33.93]</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">9.09 [6.06-18.18]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui Rural</t>
+    <t xml:space="preserve">kitui rural</t>
   </si>
   <si>
     <t xml:space="preserve">4.9 [0-7.63]</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">6.25 [4.76-11.11]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui South</t>
+    <t xml:space="preserve">kitui south</t>
   </si>
   <si>
     <t xml:space="preserve">8.01 [0-23.81]</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">9.3 [4.35-14.29]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui West</t>
+    <t xml:space="preserve">kitui west</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-9.32]</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">14.29 [0-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mwingi Central</t>
+    <t xml:space="preserve">mwingi central</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-18.33]</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">12.5 [5-27.27]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mwingi North</t>
+    <t xml:space="preserve">mwingi north</t>
   </si>
   <si>
     <t xml:space="preserve">5.26 [3.7-11.74]</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">5.26 [4-10]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mwingi West</t>
+    <t xml:space="preserve">mwingi west</t>
   </si>
   <si>
     <t xml:space="preserve">Laikipia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia East</t>
+    <t xml:space="preserve">laikipia east</t>
   </si>
   <si>
     <t xml:space="preserve">4.36 [0-7.77]</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">6.9 [3.57-14.81]</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia North</t>
+    <t xml:space="preserve">laikipia north</t>
   </si>
   <si>
     <t xml:space="preserve">10.56 [5.88-13.64]</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">5.88 [0-14.29]</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia West</t>
+    <t xml:space="preserve">laikipia west</t>
   </si>
   <si>
     <t xml:space="preserve">2 [1-2.25]</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">Machakos County</t>
   </si>
   <si>
-    <t xml:space="preserve">Athi River</t>
+    <t xml:space="preserve">mavoko</t>
   </si>
   <si>
     <t xml:space="preserve">4 [3-6]</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">33.33 [22.22-40]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalama</t>
+    <t xml:space="preserve">kalama</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-2]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kangundo</t>
+    <t xml:space="preserve">kangundo</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-9.09]</t>
   </si>
   <si>
-    <t xml:space="preserve">Machakos</t>
+    <t xml:space="preserve">machakos</t>
   </si>
   <si>
     <t xml:space="preserve">3.57 [0-18.06]</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">6.25 [0-12.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Masinga</t>
+    <t xml:space="preserve">masinga</t>
   </si>
   <si>
     <t xml:space="preserve">4.35 [0-8.89]</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">3.85 [0-4.76]</t>
   </si>
   <si>
-    <t xml:space="preserve">Matungulu</t>
+    <t xml:space="preserve">matungulu</t>
   </si>
   <si>
     <t xml:space="preserve">9.09 [0-18.75]</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">11.76 [8.33-21.05]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mwala</t>
+    <t xml:space="preserve">mwala</t>
   </si>
   <si>
     <t xml:space="preserve">5.41 [0-14.56]</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.17 [3.57-12.9]</t>
   </si>
   <si>
-    <t xml:space="preserve">Yatta</t>
+    <t xml:space="preserve">yatta</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0.75-1.25]</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">Makueni County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaiti</t>
+    <t xml:space="preserve">kaiti</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-4]</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">5.26 [0-12.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Makueni</t>
+    <t xml:space="preserve">makueni</t>
   </si>
   <si>
     <t xml:space="preserve">2 [0.75-2]</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">Marsabit County</t>
   </si>
   <si>
-    <t xml:space="preserve">North Horr</t>
+    <t xml:space="preserve">north horr</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-33.33]</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">Meru County</t>
   </si>
   <si>
-    <t xml:space="preserve">Igembe North</t>
+    <t xml:space="preserve">igembe north</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-10]</t>
   </si>
   <si>
-    <t xml:space="preserve">Imenti Central</t>
+    <t xml:space="preserve">cental imenti</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-22.5]</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">10 [0-18.18]</t>
   </si>
   <si>
-    <t xml:space="preserve">Tigania West</t>
+    <t xml:space="preserve">tigania west</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-10.28]</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">Migori County</t>
   </si>
   <si>
-    <t xml:space="preserve">Awendo</t>
+    <t xml:space="preserve">awendo</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [0-3.25]</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">20 [9.09-30.77]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kuria East</t>
+    <t xml:space="preserve">kuria east</t>
   </si>
   <si>
     <t xml:space="preserve">13.81 [7.14-23.56]</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">21.43 [14.29-23.53]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kuria West</t>
+    <t xml:space="preserve">kuria west</t>
   </si>
   <si>
     <t xml:space="preserve">2 [0.75-3]</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">20 [15.38-26.32]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyatike</t>
+    <t xml:space="preserve">nyatike</t>
   </si>
   <si>
     <t xml:space="preserve">2.5 [0-4]</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">20.59 [13.04-38.1]</t>
   </si>
   <si>
-    <t xml:space="preserve">Rongo</t>
+    <t xml:space="preserve">rongo</t>
   </si>
   <si>
     <t xml:space="preserve">18.18 [9.09-30]</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">22.22 [0-42.86]</t>
   </si>
   <si>
-    <t xml:space="preserve">Suna East</t>
+    <t xml:space="preserve">suna east</t>
   </si>
   <si>
     <t xml:space="preserve">9.09 [0-11.11]</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">13.39 [10.83-36.36]</t>
   </si>
   <si>
-    <t xml:space="preserve">Suna West</t>
+    <t xml:space="preserve">suna west</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [0.75-2.25]</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">33.33 [15.79-44.44]</t>
   </si>
   <si>
-    <t xml:space="preserve">Uriri</t>
+    <t xml:space="preserve">uriri</t>
   </si>
   <si>
     <t xml:space="preserve">2.5 [0.75-4]</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">Mombasa County</t>
   </si>
   <si>
-    <t xml:space="preserve">Changamwe</t>
+    <t xml:space="preserve">changamwe</t>
   </si>
   <si>
     <t xml:space="preserve">14.29 [0-33.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Jomvu</t>
+    <t xml:space="preserve">jomvu</t>
   </si>
   <si>
     <t xml:space="preserve">5 [0-33.33]</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">14.29 [11.11-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Likoni</t>
+    <t xml:space="preserve">likoni</t>
   </si>
   <si>
     <t xml:space="preserve">3 [0-5]</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">25 [0-33.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mvita</t>
+    <t xml:space="preserve">mvita</t>
   </si>
   <si>
     <t xml:space="preserve">14.29 [5-23.61]</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">Nairobi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Dagoretti South</t>
+    <t xml:space="preserve">dagoretti south</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-25]</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">18.18 [14.29-22.22]</t>
   </si>
   <si>
-    <t xml:space="preserve">Embakasi Central</t>
+    <t xml:space="preserve">embakasi central</t>
   </si>
   <si>
     <t xml:space="preserve">18.18 [0-28.57]</t>
   </si>
   <si>
-    <t xml:space="preserve">Embakasi South</t>
+    <t xml:space="preserve">embakasi south</t>
   </si>
   <si>
     <t xml:space="preserve">14.29 [0-28.75]</t>
   </si>
   <si>
-    <t xml:space="preserve">Embakasi West</t>
+    <t xml:space="preserve">embakasi west</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-11.11]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kamukunji</t>
+    <t xml:space="preserve">kamukunji</t>
   </si>
   <si>
     <t xml:space="preserve">6.9 [0-12.71]</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">12.5 [8.33-15.38]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kasarani</t>
+    <t xml:space="preserve">kasarani</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-21.25]</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">16.67 [14.29-33.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mathare</t>
+    <t xml:space="preserve">mathare</t>
   </si>
   <si>
     <t xml:space="preserve">1 [1-1]</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">14.29 [14.29-22.22]</t>
   </si>
   <si>
-    <t xml:space="preserve">Roysambu</t>
+    <t xml:space="preserve">roysambu</t>
   </si>
   <si>
     <t xml:space="preserve">23.61 [5.77-33.33]</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">25 [12.5-30]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ruaraka</t>
+    <t xml:space="preserve">ruaraka</t>
   </si>
   <si>
     <t xml:space="preserve">11.11 [0-21.33]</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">20 [16.67-30]</t>
   </si>
   <si>
-    <t xml:space="preserve">Starehe</t>
+    <t xml:space="preserve">starehe</t>
   </si>
   <si>
     <t xml:space="preserve">7.74 [0-16.67]</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">15.38 [7.69-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Westlands</t>
+    <t xml:space="preserve">westlands</t>
   </si>
   <si>
     <t xml:space="preserve">12.5 [7.14-21.43]</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">Nakuru County</t>
   </si>
   <si>
-    <t xml:space="preserve">Gilgil</t>
+    <t xml:space="preserve">gilgil</t>
   </si>
   <si>
     <t xml:space="preserve">8.05 [4.57-14.23]</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">9.09 [0-18.18]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kuresoi North</t>
+    <t xml:space="preserve">kuresoi north</t>
   </si>
   <si>
     <t xml:space="preserve">4.03 [0-7.94]</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">16.67 [14.29-19.05]</t>
   </si>
   <si>
-    <t xml:space="preserve">Molo</t>
+    <t xml:space="preserve">molo</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-5.64]</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">17.65 [5.56-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Naivasha</t>
+    <t xml:space="preserve">naivasha</t>
   </si>
   <si>
     <t xml:space="preserve">6.11 [4.55-10.13]</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">9.09 [8-13.04]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakuru East</t>
+    <t xml:space="preserve">nakuru town east</t>
   </si>
   <si>
     <t xml:space="preserve">5.9 [0-18.06]</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">10.53 [6.9-19.05]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakuru North</t>
+    <t xml:space="preserve">nakuru north</t>
   </si>
   <si>
     <t xml:space="preserve">4.55 [0-10.67]</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">16 [10.53-35.29]</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakuru West</t>
+    <t xml:space="preserve">nakuru town west</t>
   </si>
   <si>
     <t xml:space="preserve">3.12 [0-11.11]</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">20 [13.33-27.27]</t>
   </si>
   <si>
-    <t xml:space="preserve">Njoro</t>
+    <t xml:space="preserve">njoro</t>
   </si>
   <si>
     <t xml:space="preserve">4 [1-6]</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">16.67 [12.52-25.69]</t>
   </si>
   <si>
-    <t xml:space="preserve">Rongai</t>
+    <t xml:space="preserve">rongai</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-7.85]</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.53 [5-14.29]</t>
   </si>
   <si>
-    <t xml:space="preserve">Subukia</t>
+    <t xml:space="preserve">subukia</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-5.07]</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">Nandi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldai</t>
+    <t xml:space="preserve">aldai</t>
   </si>
   <si>
     <t xml:space="preserve">7.42 [5.56-11.76]</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">11.76 [9.52-18.75]</t>
   </si>
   <si>
-    <t xml:space="preserve">Chesumei</t>
+    <t xml:space="preserve">chesumei</t>
   </si>
   <si>
     <t xml:space="preserve">5.13 [0-11.9]</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">6.67 [0-11.11]</t>
   </si>
   <si>
-    <t xml:space="preserve">Emgwen</t>
+    <t xml:space="preserve">emgwen</t>
   </si>
   <si>
     <t xml:space="preserve">7.69 [0-10]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mosop</t>
+    <t xml:space="preserve">mosop</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 [0-1.25]</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">11.76 [0-22.22]</t>
   </si>
   <si>
-    <t xml:space="preserve">Tinderet</t>
+    <t xml:space="preserve">tinderet</t>
   </si>
   <si>
     <t xml:space="preserve">2.94 [0-13.85]</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">Narok County</t>
   </si>
   <si>
-    <t xml:space="preserve">Narok Central</t>
+    <t xml:space="preserve">narok central</t>
   </si>
   <si>
     <t xml:space="preserve">13.81 [8.9-27.08]</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">Nyandarua County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kinangop</t>
+    <t xml:space="preserve">kinangop</t>
   </si>
   <si>
     <t xml:space="preserve">11.11 [7.14-19.33]</t>
@@ -1526,16 +1526,16 @@
     <t xml:space="preserve">14.29 [7.69-26.32]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ndaragwa</t>
+    <t xml:space="preserve">ndaragwa</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-4.76]</t>
   </si>
   <si>
-    <t xml:space="preserve">Oljoroorok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olkalou</t>
+    <t xml:space="preserve">ol jorok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ol kalou</t>
   </si>
   <si>
     <t xml:space="preserve">9.09 [0-37.5]</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">Samburu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu Central</t>
+    <t xml:space="preserve">samburu central</t>
   </si>
   <si>
     <t xml:space="preserve">5 [0-15.48]</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu East</t>
+    <t xml:space="preserve">samburu east</t>
   </si>
   <si>
     <t xml:space="preserve">17.42 [7.28-31.82]</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">12.5 [6.67-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu North</t>
+    <t xml:space="preserve">samburu north</t>
   </si>
   <si>
     <t xml:space="preserve">8.33 [0-15.71]</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">Siaya County</t>
   </si>
   <si>
-    <t xml:space="preserve">Alego Usonga</t>
+    <t xml:space="preserve">alego usonga</t>
   </si>
   <si>
     <t xml:space="preserve">3 [0.75-6]</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">22.73 [19.05-30]</t>
   </si>
   <si>
-    <t xml:space="preserve">Bondo</t>
+    <t xml:space="preserve">bondo</t>
   </si>
   <si>
     <t xml:space="preserve">7.85 [3.96-19.42]</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">15 [8-34.78]</t>
   </si>
   <si>
-    <t xml:space="preserve">Gem</t>
+    <t xml:space="preserve">gem</t>
   </si>
   <si>
     <t xml:space="preserve">4 [1-9]</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">25.93 [11.76-46.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Rarieda</t>
+    <t xml:space="preserve">rarieda</t>
   </si>
   <si>
     <t xml:space="preserve">4.2 [0-8.79]</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">9.33 [0-20.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ugenya</t>
+    <t xml:space="preserve">ugenya</t>
   </si>
   <si>
     <t xml:space="preserve">17.42 [6.47-36.89]</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">33.33 [13.84-39.56]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ugunja</t>
+    <t xml:space="preserve">ugunja</t>
   </si>
   <si>
     <t xml:space="preserve">8.71 [0-23.33]</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">Taita Taveta County</t>
   </si>
   <si>
-    <t xml:space="preserve">Mwatate</t>
+    <t xml:space="preserve">mwatate</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [0.75-2]</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">18.18 [9.09-26.32]</t>
   </si>
   <si>
-    <t xml:space="preserve">Voi</t>
+    <t xml:space="preserve">voi</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-10.42]</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">Tharaka Nithi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuka</t>
+    <t xml:space="preserve">chuka</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-9.94]</t>
@@ -1670,28 +1670,28 @@
     <t xml:space="preserve">7.69 [5.88-13.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Igambangombe</t>
+    <t xml:space="preserve">igambangombe</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-1.92]</t>
   </si>
   <si>
-    <t xml:space="preserve">Maara</t>
+    <t xml:space="preserve">maara</t>
   </si>
   <si>
     <t xml:space="preserve">5.56 [0-8.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Muthambi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tharaka North</t>
+    <t xml:space="preserve">muthambi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tharaka north</t>
   </si>
   <si>
     <t xml:space="preserve">Trans Nzoia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Cherangany</t>
+    <t xml:space="preserve">cherangany</t>
   </si>
   <si>
     <t xml:space="preserve">5 [3-5]</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">18.18 [12-27.27]</t>
   </si>
   <si>
-    <t xml:space="preserve">Endebess</t>
+    <t xml:space="preserve">endebess</t>
   </si>
   <si>
     <t xml:space="preserve">8.01 [0-16.54]</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">25 [14.29-28.57]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kiminini</t>
+    <t xml:space="preserve">kiminini</t>
   </si>
   <si>
     <t xml:space="preserve">3 [2-6]</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">16.67 [8.33-31.25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kwanza</t>
+    <t xml:space="preserve">kwanza</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-23.33]</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">22.22 [14.29-27.78]</t>
   </si>
   <si>
-    <t xml:space="preserve">Saboti</t>
+    <t xml:space="preserve">saboti</t>
   </si>
   <si>
     <t xml:space="preserve">15.48 [0-38.33]</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">Turkana County</t>
   </si>
   <si>
-    <t xml:space="preserve">Aroo</t>
+    <t xml:space="preserve">aroo</t>
   </si>
   <si>
     <t xml:space="preserve">7.74 [0-16.54]</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">18.18 [16.67-33.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Loima</t>
+    <t xml:space="preserve">loima</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-1.25]</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">14.29 [9.09-20]</t>
   </si>
   <si>
-    <t xml:space="preserve">Lokichoggio</t>
+    <t xml:space="preserve">lokichoggio</t>
   </si>
   <si>
     <t xml:space="preserve">25 [0-100]</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana Central</t>
+    <t xml:space="preserve">turkana central</t>
   </si>
   <si>
     <t xml:space="preserve">8.7 [5.2-15.95]</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">11.76 [10.53-15.79]</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana East</t>
+    <t xml:space="preserve">turkana east</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-8.71]</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana South</t>
+    <t xml:space="preserve">turkana south</t>
   </si>
   <si>
     <t xml:space="preserve">10.56 [0-16.67]</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">16.67 [14.29-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana West</t>
+    <t xml:space="preserve">turkana west</t>
   </si>
   <si>
     <t xml:space="preserve">Uasin Gishu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ainabkoi</t>
+    <t xml:space="preserve">ainabkoi</t>
   </si>
   <si>
     <t xml:space="preserve">6.07 [0-11.46]</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">27.78 [24-37.5]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapseret</t>
+    <t xml:space="preserve">kapseret</t>
   </si>
   <si>
     <t xml:space="preserve">7.14 [0-10.28]</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">20 [14.29-26.32]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kesses</t>
+    <t xml:space="preserve">kesses</t>
   </si>
   <si>
     <t xml:space="preserve">8.33 [0-11.46]</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">10 [7.69-26.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Soy</t>
+    <t xml:space="preserve">soy</t>
   </si>
   <si>
     <t xml:space="preserve">7.14 [0-16.67]</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">17.16 [10.61-23.19]</t>
   </si>
   <si>
-    <t xml:space="preserve">Turbo</t>
+    <t xml:space="preserve">turbo</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [1-2.25]</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">Vihiga County</t>
   </si>
   <si>
-    <t xml:space="preserve">Emuhaya</t>
+    <t xml:space="preserve">emuhaya</t>
   </si>
   <si>
     <t xml:space="preserve">20 [0-25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamisi</t>
+    <t xml:space="preserve">hamisi</t>
   </si>
   <si>
     <t xml:space="preserve">4.88 [0-9.32]</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">7.69 [5.26-16.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Luanda</t>
+    <t xml:space="preserve">luanda</t>
   </si>
   <si>
     <t xml:space="preserve">3.33 [0-7.44]</t>
   </si>
   <si>
-    <t xml:space="preserve">Sabatia</t>
+    <t xml:space="preserve">sabatia</t>
   </si>
   <si>
     <t xml:space="preserve">7.14 [0-16.11]</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">18.18 [0-30]</t>
   </si>
   <si>
-    <t xml:space="preserve">Vihiga</t>
+    <t xml:space="preserve">vihiga</t>
   </si>
   <si>
     <t xml:space="preserve">10 [0-16.67]</t>
